--- a/mappingCorps/ig/FRObservationLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRObservationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,79 +118,109 @@
     <t>FRCDASimpleObservation</t>
   </si>
   <si>
-    <t>FRLMObservation.observationIdentifiant</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.id</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationCode</t>
+    <t>FRLMObservation.header.status</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMObservation.header.directSubject[x]</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.subject</t>
+  </si>
+  <si>
+    <t>FRLMObservation.observationDate[x]</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMObservation.type</t>
   </si>
   <si>
     <t>FRCDASimpleObservation.code</t>
   </si>
   <si>
-    <t>FRLMObservation.observationDescription</t>
+    <t>FRLMObservation.originalName</t>
   </si>
   <si>
     <t>FRCDASimpleObservation.text</t>
   </si>
   <si>
-    <t>FRLMObservation.observationStatut</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationDate</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationResultat</t>
+    <t>FRLMObservation.method</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.methodCode</t>
+  </si>
+  <si>
+    <t>FRLMObservation.specimen</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.specimen</t>
+  </si>
+  <si>
+    <t>FRLMObservation.order</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.inFulfillmentOf</t>
+  </si>
+  <si>
+    <t>FRLMObservation.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.targetSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMObservation.result</t>
   </si>
   <si>
     <t>FRCDASimpleObservation.value</t>
   </si>
   <si>
-    <t>FRLMObservation.observationInterpretation</t>
+    <t>FRLMObservation.referenceRange</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.referenceRange</t>
+  </si>
+  <si>
+    <t>FRLMObservation.interpretation</t>
   </si>
   <si>
     <t>FRCDASimpleObservation.interpretationCode</t>
   </si>
   <si>
-    <t>FRLMObservation.observationMethode</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.methodCode</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationLocalisationAnatomique</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationAuteur</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.author</t>
-  </si>
-  <si>
-    <t>FRLMObservation.observationNombreRenouvellements</t>
-  </si>
-  <si>
-    <t>FRCDASimpleObservation.repeatNumber</t>
+    <t>FRLMObservation.note</t>
+  </si>
+  <si>
+    <t>FRLMObservation.derivedFrom[x]</t>
+  </si>
+  <si>
+    <t>FRCDASimpleObservation.entryRelationship</t>
+  </si>
+  <si>
+    <t>FRLMObservation.hasMember[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-ml-observation</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/R4/StructureDefinition/Observation</t>
   </si>
   <si>
+    <t>FRMLObservation</t>
+  </si>
+  <si>
     <t>Observation</t>
   </si>
   <si>
-    <t>Observation.identifier</t>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -199,25 +229,37 @@
     <t>Observation.note</t>
   </si>
   <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t>Observation.basedOn</t>
+  </si>
+  <si>
+    <t>Observation.bodySite</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
   </si>
   <si>
+    <t>Observation.referenceRange</t>
+  </si>
+  <si>
     <t>Observation.interpretation</t>
   </si>
   <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
+    <t>FRLMObservation.component</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom</t>
+  </si>
+  <si>
+    <t>Observation.hasMember</t>
   </si>
 </sst>
 </file>
@@ -469,7 +511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -661,6 +703,58 @@
         <v>55</v>
       </c>
       <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -669,7 +763,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -691,7 +785,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -700,7 +794,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -708,146 +802,224 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
